--- a/data_VR4.xlsx
+++ b/data_VR4.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\y0808\search-app\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C5A5B0C-2244-4B64-A7CF-F76843BA1ED6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6019C19-0492-4920-916E-9B7DEE06E7AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3072" yWindow="3072" windowWidth="17280" windowHeight="9420" xr2:uid="{51A6361B-5262-4E40-ACE6-80335589EBEA}"/>
+    <workbookView xWindow="3072" yWindow="1944" windowWidth="17280" windowHeight="9420" xr2:uid="{51A6361B-5262-4E40-ACE6-80335589EBEA}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="7">
   <si>
     <t>table</t>
     <phoneticPr fontId="1"/>
@@ -49,6 +49,14 @@
   </si>
   <si>
     <t>P-LR</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>P-66</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>P-36</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -1863,6 +1871,12 @@
       <c r="B2">
         <v>1</v>
       </c>
+      <c r="C2">
+        <v>48</v>
+      </c>
+      <c r="D2">
+        <v>30</v>
+      </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A3">
@@ -1871,6 +1885,12 @@
       <c r="B3">
         <v>2</v>
       </c>
+      <c r="C3">
+        <v>62</v>
+      </c>
+      <c r="D3">
+        <v>34</v>
+      </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A4">
@@ -1879,6 +1899,12 @@
       <c r="B4">
         <v>3</v>
       </c>
+      <c r="C4">
+        <v>8</v>
+      </c>
+      <c r="D4">
+        <v>26</v>
+      </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A5">
@@ -1887,6 +1913,12 @@
       <c r="B5">
         <v>4</v>
       </c>
+      <c r="C5">
+        <v>43</v>
+      </c>
+      <c r="D5">
+        <v>10</v>
+      </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A6">
@@ -1895,6 +1927,12 @@
       <c r="B6">
         <v>5</v>
       </c>
+      <c r="C6">
+        <v>51</v>
+      </c>
+      <c r="D6">
+        <v>33</v>
+      </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A7">
@@ -1903,6 +1941,12 @@
       <c r="B7">
         <v>6</v>
       </c>
+      <c r="C7">
+        <v>34</v>
+      </c>
+      <c r="D7">
+        <v>60</v>
+      </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A8">
@@ -1911,6 +1955,12 @@
       <c r="B8">
         <v>7</v>
       </c>
+      <c r="C8">
+        <v>27</v>
+      </c>
+      <c r="D8">
+        <v>23</v>
+      </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A9">
@@ -1919,6 +1969,12 @@
       <c r="B9">
         <v>8</v>
       </c>
+      <c r="C9">
+        <v>60</v>
+      </c>
+      <c r="D9">
+        <v>70</v>
+      </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A10">
@@ -1927,6 +1983,12 @@
       <c r="B10">
         <v>9</v>
       </c>
+      <c r="C10">
+        <v>38</v>
+      </c>
+      <c r="D10">
+        <v>51</v>
+      </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A11">
@@ -1935,6 +1997,12 @@
       <c r="B11">
         <v>10</v>
       </c>
+      <c r="C11">
+        <v>44</v>
+      </c>
+      <c r="D11">
+        <v>37</v>
+      </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A12">
@@ -1943,6 +2011,12 @@
       <c r="B12">
         <v>11</v>
       </c>
+      <c r="C12">
+        <v>52</v>
+      </c>
+      <c r="D12">
+        <v>16</v>
+      </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A13">
@@ -1951,6 +2025,12 @@
       <c r="B13">
         <v>12</v>
       </c>
+      <c r="C13">
+        <v>50</v>
+      </c>
+      <c r="D13">
+        <v>22</v>
+      </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A14">
@@ -1959,6 +2039,12 @@
       <c r="B14">
         <v>13</v>
       </c>
+      <c r="C14">
+        <v>18</v>
+      </c>
+      <c r="D14">
+        <v>15</v>
+      </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A15">
@@ -1967,6 +2053,12 @@
       <c r="B15">
         <v>14</v>
       </c>
+      <c r="C15">
+        <v>10</v>
+      </c>
+      <c r="D15">
+        <v>31</v>
+      </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A16">
@@ -1975,685 +2067,1201 @@
       <c r="B16">
         <v>15</v>
       </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C16">
+        <v>39</v>
+      </c>
+      <c r="D16">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A17">
         <v>1</v>
       </c>
       <c r="B17">
         <v>16</v>
       </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C17">
+        <v>63</v>
+      </c>
+      <c r="D17">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A18">
         <v>1</v>
       </c>
       <c r="B18">
         <v>17</v>
       </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C18">
+        <v>33</v>
+      </c>
+      <c r="D18">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A19">
         <v>1</v>
       </c>
       <c r="B19">
         <v>18</v>
       </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C19">
+        <v>12</v>
+      </c>
+      <c r="D19">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A20">
         <v>1</v>
       </c>
       <c r="B20">
         <v>19</v>
       </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C20">
+        <v>11</v>
+      </c>
+      <c r="D20">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A21">
         <v>1</v>
       </c>
       <c r="B21">
         <v>20</v>
       </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C21">
+        <v>20</v>
+      </c>
+      <c r="D21">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A22">
         <v>1</v>
       </c>
       <c r="B22">
         <v>21</v>
       </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C22">
+        <v>45</v>
+      </c>
+      <c r="D22">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A23">
         <v>1</v>
       </c>
       <c r="B23">
         <v>22</v>
       </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C23">
+        <v>42</v>
+      </c>
+      <c r="D23">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A24">
         <v>1</v>
       </c>
       <c r="B24">
         <v>23</v>
       </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C24">
+        <v>26</v>
+      </c>
+      <c r="D24">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A25">
         <v>1</v>
       </c>
       <c r="B25">
         <v>24</v>
       </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C25">
+        <v>6</v>
+      </c>
+      <c r="D25">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A26">
         <v>1</v>
       </c>
       <c r="B26">
         <v>25</v>
       </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C26">
+        <v>28</v>
+      </c>
+      <c r="D26">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A27">
         <v>1</v>
       </c>
       <c r="B27">
         <v>26</v>
       </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C27">
+        <v>22</v>
+      </c>
+      <c r="D27">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A28">
         <v>1</v>
       </c>
       <c r="B28">
         <v>27</v>
       </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C28">
+        <v>7</v>
+      </c>
+      <c r="D28">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A29">
         <v>1</v>
       </c>
       <c r="B29">
         <v>28</v>
       </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C29">
+        <v>19</v>
+      </c>
+      <c r="D29">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A30">
         <v>1</v>
       </c>
       <c r="B30">
         <v>29</v>
       </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C30">
+        <v>15</v>
+      </c>
+      <c r="D30">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A31">
         <v>1</v>
       </c>
       <c r="B31">
         <v>30</v>
       </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C31">
+        <v>65</v>
+      </c>
+      <c r="D31">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A32">
         <v>1</v>
       </c>
       <c r="B32">
         <v>31</v>
       </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C32">
+        <v>3</v>
+      </c>
+      <c r="D32">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A33">
         <v>1</v>
       </c>
       <c r="B33">
         <v>32</v>
       </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C33">
+        <v>56</v>
+      </c>
+      <c r="D33">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A34">
         <v>1</v>
       </c>
       <c r="B34">
         <v>33</v>
       </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C34">
+        <v>35</v>
+      </c>
+      <c r="D34">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A35">
         <v>1</v>
       </c>
       <c r="B35">
         <v>34</v>
       </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C35">
+        <v>47</v>
+      </c>
+      <c r="D35">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A36">
         <v>1</v>
       </c>
       <c r="B36">
         <v>35</v>
       </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C36">
+        <v>14</v>
+      </c>
+      <c r="D36">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A37">
         <v>1</v>
       </c>
       <c r="B37">
         <v>36</v>
       </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C37">
+        <v>43</v>
+      </c>
+      <c r="D37">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A38">
         <v>1</v>
       </c>
       <c r="B38">
         <v>37</v>
       </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C38">
+        <v>51</v>
+      </c>
+      <c r="D38">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A39">
         <v>1</v>
       </c>
       <c r="B39">
         <v>38</v>
       </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C39">
+        <v>24</v>
+      </c>
+      <c r="D39">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A40">
         <v>1</v>
       </c>
       <c r="B40">
         <v>39</v>
       </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C40">
+        <v>48</v>
+      </c>
+      <c r="D40">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A41">
         <v>1</v>
       </c>
       <c r="B41">
         <v>40</v>
       </c>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C41">
+        <v>59</v>
+      </c>
+      <c r="D41">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A42">
         <v>1</v>
       </c>
       <c r="B42">
         <v>41</v>
       </c>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C42">
+        <v>4</v>
+      </c>
+      <c r="D42">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A43">
         <v>1</v>
       </c>
       <c r="B43">
         <v>42</v>
       </c>
-    </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C43">
+        <v>54</v>
+      </c>
+      <c r="D43">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A44">
         <v>1</v>
       </c>
       <c r="B44">
         <v>43</v>
       </c>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C44">
+        <v>30</v>
+      </c>
+      <c r="D44">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A45">
         <v>1</v>
       </c>
       <c r="B45">
         <v>44</v>
       </c>
-    </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C45">
+        <v>37</v>
+      </c>
+      <c r="D45">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A46">
         <v>1</v>
       </c>
       <c r="B46">
         <v>45</v>
       </c>
-    </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C46">
+        <v>8</v>
+      </c>
+      <c r="D46">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A47">
         <v>1</v>
       </c>
       <c r="B47">
         <v>46</v>
       </c>
-    </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C47">
+        <v>67</v>
+      </c>
+      <c r="D47">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A48">
         <v>1</v>
       </c>
       <c r="B48">
         <v>47</v>
       </c>
-    </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C48">
+        <v>18</v>
+      </c>
+      <c r="D48">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A49">
         <v>1</v>
       </c>
       <c r="B49">
         <v>48</v>
       </c>
-    </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C49">
+        <v>41</v>
+      </c>
+      <c r="D49">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A50">
         <v>1</v>
       </c>
       <c r="B50">
         <v>49</v>
       </c>
-    </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C50">
+        <v>39</v>
+      </c>
+      <c r="D50">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A51">
         <v>1</v>
       </c>
       <c r="B51">
         <v>50</v>
       </c>
-    </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C51">
+        <v>13</v>
+      </c>
+      <c r="D51">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A52">
         <v>1</v>
       </c>
       <c r="B52">
         <v>51</v>
       </c>
-    </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C52">
+        <v>38</v>
+      </c>
+      <c r="D52">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A53">
         <v>1</v>
       </c>
       <c r="B53">
         <v>52</v>
       </c>
-    </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C53">
+        <v>6</v>
+      </c>
+      <c r="D53">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A54">
         <v>1</v>
       </c>
       <c r="B54">
         <v>53</v>
       </c>
-    </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C54">
+        <v>16</v>
+      </c>
+      <c r="D54">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A55">
         <v>1</v>
       </c>
       <c r="B55">
         <v>54</v>
       </c>
-    </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C55" t="s">
+        <v>5</v>
+      </c>
+      <c r="D55">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A56">
         <v>1</v>
       </c>
       <c r="B56">
         <v>55</v>
       </c>
-    </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C56">
+        <v>23</v>
+      </c>
+      <c r="D56">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A57">
         <v>1</v>
       </c>
       <c r="B57">
         <v>56</v>
       </c>
-    </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C57">
+        <v>2</v>
+      </c>
+      <c r="D57">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A58">
         <v>1</v>
       </c>
       <c r="B58">
         <v>57</v>
       </c>
-    </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C58">
+        <v>11</v>
+      </c>
+      <c r="D58">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A59">
         <v>1</v>
       </c>
       <c r="B59">
         <v>58</v>
       </c>
-    </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C59">
+        <v>47</v>
+      </c>
+      <c r="D59">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A60">
         <v>1</v>
       </c>
       <c r="B60">
         <v>59</v>
       </c>
-    </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C60">
+        <v>33</v>
+      </c>
+      <c r="D60">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A61">
         <v>1</v>
       </c>
       <c r="B61">
         <v>60</v>
       </c>
-    </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C61">
+        <v>17</v>
+      </c>
+      <c r="D61">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A62">
         <v>1</v>
       </c>
       <c r="B62">
         <v>61</v>
       </c>
-    </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C62">
+        <v>7</v>
+      </c>
+      <c r="D62">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A63">
         <v>1</v>
       </c>
       <c r="B63">
         <v>62</v>
       </c>
-    </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C63">
+        <v>10</v>
+      </c>
+      <c r="D63">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A64">
         <v>1</v>
       </c>
       <c r="B64">
         <v>63</v>
       </c>
-    </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C64">
+        <v>27</v>
+      </c>
+      <c r="D64">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A65">
         <v>1</v>
       </c>
       <c r="B65">
         <v>64</v>
       </c>
-    </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C65">
+        <v>19</v>
+      </c>
+      <c r="D65">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A66">
         <v>1</v>
       </c>
       <c r="B66">
         <v>65</v>
       </c>
-    </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C66">
+        <v>15</v>
+      </c>
+      <c r="D66">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A67">
         <v>1</v>
       </c>
       <c r="B67">
         <v>66</v>
       </c>
-    </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C67">
+        <v>61</v>
+      </c>
+      <c r="D67">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A68">
         <v>1</v>
       </c>
       <c r="B68">
         <v>67</v>
       </c>
-    </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C68">
+        <v>26</v>
+      </c>
+      <c r="D68">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A69">
         <v>1</v>
       </c>
       <c r="B69">
         <v>68</v>
       </c>
-    </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C69">
+        <v>12</v>
+      </c>
+      <c r="D69">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A70">
         <v>1</v>
       </c>
       <c r="B70">
         <v>69</v>
       </c>
-    </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C70">
+        <v>52</v>
+      </c>
+      <c r="D70">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A71">
         <v>1</v>
       </c>
       <c r="B71">
         <v>70</v>
       </c>
-    </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C71">
+        <v>21</v>
+      </c>
+      <c r="D71">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A72">
         <v>1</v>
       </c>
       <c r="B72">
         <v>71</v>
       </c>
-    </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C72">
+        <v>3</v>
+      </c>
+      <c r="D72">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A73">
         <v>1</v>
       </c>
       <c r="B73">
         <v>72</v>
       </c>
-    </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C73">
+        <v>66</v>
+      </c>
+      <c r="D73">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A74">
         <v>1</v>
       </c>
       <c r="B74">
         <v>73</v>
       </c>
-    </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C74">
+        <v>28</v>
+      </c>
+      <c r="D74">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A75">
         <v>1</v>
       </c>
       <c r="B75">
         <v>74</v>
       </c>
-    </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C75">
+        <v>54</v>
+      </c>
+      <c r="D75">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A76">
         <v>1</v>
       </c>
       <c r="B76">
         <v>75</v>
       </c>
-    </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C76">
+        <v>14</v>
+      </c>
+      <c r="D76">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A77">
         <v>1</v>
       </c>
       <c r="B77">
         <v>76</v>
       </c>
-    </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C77">
+        <v>60</v>
+      </c>
+      <c r="D77">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A78">
         <v>1</v>
       </c>
       <c r="B78">
         <v>77</v>
       </c>
-    </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C78">
+        <v>4</v>
+      </c>
+      <c r="D78">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A79">
         <v>1</v>
       </c>
       <c r="B79">
         <v>78</v>
       </c>
-    </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C79">
+        <v>69</v>
+      </c>
+      <c r="D79">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A80">
         <v>1</v>
       </c>
       <c r="B80">
         <v>79</v>
       </c>
-    </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C80">
+        <v>30</v>
+      </c>
+      <c r="D80">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A81">
         <v>1</v>
       </c>
       <c r="B81">
         <v>80</v>
       </c>
-    </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C81">
+        <v>20</v>
+      </c>
+      <c r="D81">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A82">
         <v>1</v>
       </c>
       <c r="B82">
         <v>81</v>
       </c>
-    </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C82">
+        <v>38</v>
+      </c>
+      <c r="D82">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A83">
         <v>1</v>
       </c>
       <c r="B83">
         <v>82</v>
       </c>
-    </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C83">
+        <v>56</v>
+      </c>
+      <c r="D83">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A84">
         <v>1</v>
       </c>
       <c r="B84">
         <v>83</v>
       </c>
-    </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C84">
+        <v>8</v>
+      </c>
+      <c r="D84">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A85">
         <v>1</v>
       </c>
       <c r="B85">
         <v>84</v>
       </c>
-    </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C85">
+        <v>49</v>
+      </c>
+      <c r="D85">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A86">
         <v>1</v>
       </c>
       <c r="B86">
         <v>85</v>
       </c>
-    </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C86">
+        <v>39</v>
+      </c>
+      <c r="D86">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A87">
         <v>1</v>
       </c>
       <c r="B87">
         <v>86</v>
       </c>
-    </row>
-    <row r="88" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C87">
+        <v>37</v>
+      </c>
+      <c r="D87">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A88">
         <v>1</v>
       </c>
       <c r="B88">
         <v>87</v>
       </c>
-    </row>
-    <row r="89" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C88">
+        <v>35</v>
+      </c>
+      <c r="D88">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A89">
         <v>1</v>
       </c>
       <c r="B89">
         <v>88</v>
       </c>
-    </row>
-    <row r="90" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C89">
+        <v>2</v>
+      </c>
+      <c r="D89">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A90">
         <v>1</v>
       </c>
       <c r="B90">
         <v>89</v>
       </c>
-    </row>
-    <row r="91" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C90">
+        <v>48</v>
+      </c>
+      <c r="D90">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A91">
         <v>1</v>
       </c>
       <c r="B91">
         <v>90</v>
       </c>
-    </row>
-    <row r="92" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C91">
+        <v>9</v>
+      </c>
+      <c r="D91">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A92">
         <v>1</v>
       </c>
       <c r="B92">
         <v>91</v>
       </c>
-    </row>
-    <row r="93" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C92">
+        <v>16</v>
+      </c>
+      <c r="D92">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A93">
         <v>1</v>
       </c>
       <c r="B93">
         <v>92</v>
       </c>
-    </row>
-    <row r="94" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C93">
+        <v>50</v>
+      </c>
+      <c r="D93">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A94">
         <v>1</v>
       </c>
       <c r="B94">
         <v>93</v>
       </c>
-    </row>
-    <row r="95" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C94">
+        <v>23</v>
+      </c>
+      <c r="D94">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A95">
         <v>1</v>
       </c>
       <c r="B95">
         <v>94</v>
       </c>
-    </row>
-    <row r="96" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C95">
+        <v>41</v>
+      </c>
+      <c r="D95">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="96" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A96">
         <v>1</v>
       </c>
       <c r="B96">
         <v>95</v>
       </c>
-    </row>
-    <row r="97" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C96">
+        <v>26</v>
+      </c>
+      <c r="D96">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A97">
         <v>1</v>
       </c>
       <c r="B97">
         <v>96</v>
       </c>
-    </row>
-    <row r="98" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C97">
+        <v>59</v>
+      </c>
+      <c r="D97">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="98" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A98">
         <v>1</v>
       </c>
       <c r="B98">
         <v>97</v>
       </c>
-    </row>
-    <row r="99" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C98">
+        <v>45</v>
+      </c>
+      <c r="D98">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="99" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A99">
         <v>1</v>
       </c>
       <c r="B99">
         <v>98</v>
       </c>
-    </row>
-    <row r="100" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C99">
+        <v>68</v>
+      </c>
+      <c r="D99">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="100" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A100">
         <v>1</v>
       </c>
       <c r="B100">
         <v>99</v>
       </c>
-    </row>
-    <row r="101" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C100">
+        <v>15</v>
+      </c>
+      <c r="D100">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="101" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A101">
         <v>1</v>
       </c>
       <c r="B101">
         <v>100</v>
+      </c>
+      <c r="C101">
+        <v>34</v>
+      </c>
+      <c r="D101">
+        <v>57</v>
       </c>
     </row>
   </sheetData>
@@ -2688,6 +3296,12 @@
       <c r="B2">
         <v>1</v>
       </c>
+      <c r="C2">
+        <v>16</v>
+      </c>
+      <c r="D2">
+        <v>35</v>
+      </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A3">
@@ -2696,6 +3310,12 @@
       <c r="B3">
         <v>2</v>
       </c>
+      <c r="C3">
+        <v>6</v>
+      </c>
+      <c r="D3">
+        <v>54</v>
+      </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A4">
@@ -2704,6 +3324,12 @@
       <c r="B4">
         <v>3</v>
       </c>
+      <c r="C4">
+        <v>35</v>
+      </c>
+      <c r="D4">
+        <v>33</v>
+      </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A5">
@@ -2712,6 +3338,12 @@
       <c r="B5">
         <v>4</v>
       </c>
+      <c r="C5">
+        <v>59</v>
+      </c>
+      <c r="D5">
+        <v>37</v>
+      </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A6">
@@ -2720,6 +3352,12 @@
       <c r="B6">
         <v>5</v>
       </c>
+      <c r="C6">
+        <v>15</v>
+      </c>
+      <c r="D6">
+        <v>45</v>
+      </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A7">
@@ -2728,6 +3366,12 @@
       <c r="B7">
         <v>6</v>
       </c>
+      <c r="C7">
+        <v>64</v>
+      </c>
+      <c r="D7">
+        <v>68</v>
+      </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A8">
@@ -2736,6 +3380,12 @@
       <c r="B8">
         <v>7</v>
       </c>
+      <c r="C8">
+        <v>52</v>
+      </c>
+      <c r="D8">
+        <v>39</v>
+      </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A9">
@@ -2744,6 +3394,12 @@
       <c r="B9">
         <v>8</v>
       </c>
+      <c r="C9">
+        <v>34</v>
+      </c>
+      <c r="D9">
+        <v>34</v>
+      </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A10">
@@ -2752,6 +3408,12 @@
       <c r="B10">
         <v>9</v>
       </c>
+      <c r="C10">
+        <v>8</v>
+      </c>
+      <c r="D10">
+        <v>28</v>
+      </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A11">
@@ -2760,6 +3422,12 @@
       <c r="B11">
         <v>10</v>
       </c>
+      <c r="C11">
+        <v>22</v>
+      </c>
+      <c r="D11">
+        <v>47</v>
+      </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A12">
@@ -2768,6 +3436,12 @@
       <c r="B12">
         <v>11</v>
       </c>
+      <c r="C12">
+        <v>14</v>
+      </c>
+      <c r="D12">
+        <v>3</v>
+      </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A13">
@@ -2776,6 +3450,12 @@
       <c r="B13">
         <v>12</v>
       </c>
+      <c r="C13">
+        <v>60</v>
+      </c>
+      <c r="D13">
+        <v>53</v>
+      </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A14">
@@ -2784,6 +3464,12 @@
       <c r="B14">
         <v>13</v>
       </c>
+      <c r="C14">
+        <v>30</v>
+      </c>
+      <c r="D14">
+        <v>38</v>
+      </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A15">
@@ -2792,6 +3478,12 @@
       <c r="B15">
         <v>14</v>
       </c>
+      <c r="C15">
+        <v>69</v>
+      </c>
+      <c r="D15">
+        <v>20</v>
+      </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A16">
@@ -2800,685 +3492,1201 @@
       <c r="B16">
         <v>15</v>
       </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C16">
+        <v>18</v>
+      </c>
+      <c r="D16">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A17">
         <v>1</v>
       </c>
       <c r="B17">
         <v>16</v>
       </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C17">
+        <v>41</v>
+      </c>
+      <c r="D17">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A18">
         <v>1</v>
       </c>
       <c r="B18">
         <v>17</v>
       </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C18">
+        <v>51</v>
+      </c>
+      <c r="D18">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A19">
         <v>1</v>
       </c>
       <c r="B19">
         <v>18</v>
       </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C19">
+        <v>6</v>
+      </c>
+      <c r="D19">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A20">
         <v>1</v>
       </c>
       <c r="B20">
         <v>19</v>
       </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C20">
+        <v>7</v>
+      </c>
+      <c r="D20">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A21">
         <v>1</v>
       </c>
       <c r="B21">
         <v>20</v>
       </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C21">
+        <v>19</v>
+      </c>
+      <c r="D21">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A22">
         <v>1</v>
       </c>
       <c r="B22">
         <v>21</v>
       </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C22">
+        <v>39</v>
+      </c>
+      <c r="D22">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A23">
         <v>1</v>
       </c>
       <c r="B23">
         <v>22</v>
       </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C23">
+        <v>32</v>
+      </c>
+      <c r="D23">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A24">
         <v>1</v>
       </c>
       <c r="B24">
         <v>23</v>
       </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C24">
+        <v>48</v>
+      </c>
+      <c r="D24">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A25">
         <v>1</v>
       </c>
       <c r="B25">
         <v>24</v>
       </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C25">
+        <v>54</v>
+      </c>
+      <c r="D25">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A26">
         <v>1</v>
       </c>
       <c r="B26">
         <v>25</v>
       </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C26">
+        <v>27</v>
+      </c>
+      <c r="D26">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A27">
         <v>1</v>
       </c>
       <c r="B27">
         <v>26</v>
       </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C27">
+        <v>56</v>
+      </c>
+      <c r="D27">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A28">
         <v>1</v>
       </c>
       <c r="B28">
         <v>27</v>
       </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C28">
+        <v>52</v>
+      </c>
+      <c r="D28">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A29">
         <v>1</v>
       </c>
       <c r="B29">
         <v>28</v>
       </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C29">
+        <v>50</v>
+      </c>
+      <c r="D29">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A30">
         <v>1</v>
       </c>
       <c r="B30">
         <v>29</v>
       </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C30">
+        <v>4</v>
+      </c>
+      <c r="D30">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A31">
         <v>1</v>
       </c>
       <c r="B31">
         <v>30</v>
       </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C31">
+        <v>70</v>
+      </c>
+      <c r="D31">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A32">
         <v>1</v>
       </c>
       <c r="B32">
         <v>31</v>
       </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C32">
+        <v>45</v>
+      </c>
+      <c r="D32">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A33">
         <v>1</v>
       </c>
       <c r="B33">
         <v>32</v>
       </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C33">
+        <v>43</v>
+      </c>
+      <c r="D33">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A34">
         <v>1</v>
       </c>
       <c r="B34">
         <v>33</v>
       </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C34">
+        <v>28</v>
+      </c>
+      <c r="D34">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A35">
         <v>1</v>
       </c>
       <c r="B35">
         <v>34</v>
       </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C35">
+        <v>47</v>
+      </c>
+      <c r="D35">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A36">
         <v>1</v>
       </c>
       <c r="B36">
         <v>35</v>
       </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C36">
+        <v>30</v>
+      </c>
+      <c r="D36">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A37">
         <v>1</v>
       </c>
       <c r="B37">
         <v>36</v>
       </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C37">
+        <v>62</v>
+      </c>
+      <c r="D37">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A38">
         <v>1</v>
       </c>
       <c r="B38">
         <v>37</v>
       </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C38">
+        <v>15</v>
+      </c>
+      <c r="D38">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A39">
         <v>1</v>
       </c>
       <c r="B39">
         <v>38</v>
       </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C39">
+        <v>20</v>
+      </c>
+      <c r="D39">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A40">
         <v>1</v>
       </c>
       <c r="B40">
         <v>39</v>
       </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C40">
+        <v>38</v>
+      </c>
+      <c r="D40">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A41">
         <v>1</v>
       </c>
       <c r="B41">
         <v>40</v>
       </c>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C41">
+        <v>22</v>
+      </c>
+      <c r="D41">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A42">
         <v>1</v>
       </c>
       <c r="B42">
         <v>41</v>
       </c>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C42">
+        <v>3</v>
+      </c>
+      <c r="D42">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A43">
         <v>1</v>
       </c>
       <c r="B43">
         <v>42</v>
       </c>
-    </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C43">
+        <v>42</v>
+      </c>
+      <c r="D43">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A44">
         <v>1</v>
       </c>
       <c r="B44">
         <v>43</v>
       </c>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C44">
+        <v>35</v>
+      </c>
+      <c r="D44">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A45">
         <v>1</v>
       </c>
       <c r="B45">
         <v>44</v>
       </c>
-    </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C45">
+        <v>12</v>
+      </c>
+      <c r="D45">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A46">
         <v>1</v>
       </c>
       <c r="B46">
         <v>45</v>
       </c>
-    </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C46">
+        <v>39</v>
+      </c>
+      <c r="D46">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A47">
         <v>1</v>
       </c>
       <c r="B47">
         <v>46</v>
       </c>
-    </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C47">
+        <v>2</v>
+      </c>
+      <c r="D47">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A48">
         <v>1</v>
       </c>
       <c r="B48">
         <v>47</v>
       </c>
-    </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C48">
+        <v>7</v>
+      </c>
+      <c r="D48">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A49">
         <v>1</v>
       </c>
       <c r="B49">
         <v>48</v>
       </c>
-    </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C49" t="s">
+        <v>6</v>
+      </c>
+      <c r="D49">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A50">
         <v>1</v>
       </c>
       <c r="B50">
         <v>49</v>
       </c>
-    </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C50">
+        <v>16</v>
+      </c>
+      <c r="D50">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A51">
         <v>1</v>
       </c>
       <c r="B51">
         <v>50</v>
       </c>
-    </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C51">
+        <v>37</v>
+      </c>
+      <c r="D51">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A52">
         <v>1</v>
       </c>
       <c r="B52">
         <v>51</v>
       </c>
-    </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C52">
+        <v>14</v>
+      </c>
+      <c r="D52">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A53">
         <v>1</v>
       </c>
       <c r="B53">
         <v>52</v>
       </c>
-    </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C53">
+        <v>19</v>
+      </c>
+      <c r="D53">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A54">
         <v>1</v>
       </c>
       <c r="B54">
         <v>53</v>
       </c>
-    </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C54">
+        <v>26</v>
+      </c>
+      <c r="D54">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A55">
         <v>1</v>
       </c>
       <c r="B55">
         <v>54</v>
       </c>
-    </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C55">
+        <v>44</v>
+      </c>
+      <c r="D55">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A56">
         <v>1</v>
       </c>
       <c r="B56">
         <v>55</v>
       </c>
-    </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C56">
+        <v>23</v>
+      </c>
+      <c r="D56">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A57">
         <v>1</v>
       </c>
       <c r="B57">
         <v>56</v>
       </c>
-    </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C57">
+        <v>41</v>
+      </c>
+      <c r="D57">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A58">
         <v>1</v>
       </c>
       <c r="B58">
         <v>57</v>
       </c>
-    </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C58">
+        <v>27</v>
+      </c>
+      <c r="D58">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A59">
         <v>1</v>
       </c>
       <c r="B59">
         <v>58</v>
       </c>
-    </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C59">
+        <v>34</v>
+      </c>
+      <c r="D59">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A60">
         <v>1</v>
       </c>
       <c r="B60">
         <v>59</v>
       </c>
-    </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C60">
+        <v>8</v>
+      </c>
+      <c r="D60">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A61">
         <v>1</v>
       </c>
       <c r="B61">
         <v>60</v>
       </c>
-    </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C61">
+        <v>61</v>
+      </c>
+      <c r="D61">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A62">
         <v>1</v>
       </c>
       <c r="B62">
         <v>61</v>
       </c>
-    </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C62">
+        <v>51</v>
+      </c>
+      <c r="D62">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A63">
         <v>1</v>
       </c>
       <c r="B63">
         <v>62</v>
       </c>
-    </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C63">
+        <v>21</v>
+      </c>
+      <c r="D63">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A64">
         <v>1</v>
       </c>
       <c r="B64">
         <v>63</v>
       </c>
-    </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C64">
+        <v>11</v>
+      </c>
+      <c r="D64">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A65">
         <v>1</v>
       </c>
       <c r="B65">
         <v>64</v>
       </c>
-    </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C65">
+        <v>20</v>
+      </c>
+      <c r="D65">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A66">
         <v>1</v>
       </c>
       <c r="B66">
         <v>65</v>
       </c>
-    </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C66">
+        <v>33</v>
+      </c>
+      <c r="D66">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A67">
         <v>1</v>
       </c>
       <c r="B67">
         <v>66</v>
       </c>
-    </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C67">
+        <v>68</v>
+      </c>
+      <c r="D67">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A68">
         <v>1</v>
       </c>
       <c r="B68">
         <v>67</v>
       </c>
-    </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C68">
+        <v>4</v>
+      </c>
+      <c r="D68">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A69">
         <v>1</v>
       </c>
       <c r="B69">
         <v>68</v>
       </c>
-    </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C69">
+        <v>50</v>
+      </c>
+      <c r="D69">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A70">
         <v>1</v>
       </c>
       <c r="B70">
         <v>69</v>
       </c>
-    </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C70">
+        <v>48</v>
+      </c>
+      <c r="D70">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A71">
         <v>1</v>
       </c>
       <c r="B71">
         <v>70</v>
       </c>
-    </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C71">
+        <v>54</v>
+      </c>
+      <c r="D71">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A72">
         <v>1</v>
       </c>
       <c r="B72">
         <v>71</v>
       </c>
-    </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C72">
+        <v>30</v>
+      </c>
+      <c r="D72">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A73">
         <v>1</v>
       </c>
       <c r="B73">
         <v>72</v>
       </c>
-    </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C73">
+        <v>36</v>
+      </c>
+      <c r="D73">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A74">
         <v>1</v>
       </c>
       <c r="B74">
         <v>73</v>
       </c>
-    </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C74">
+        <v>45</v>
+      </c>
+      <c r="D74">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A75">
         <v>1</v>
       </c>
       <c r="B75">
         <v>74</v>
       </c>
-    </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C75">
+        <v>43</v>
+      </c>
+      <c r="D75">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A76">
         <v>1</v>
       </c>
       <c r="B76">
         <v>75</v>
       </c>
-    </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C76">
+        <v>18</v>
+      </c>
+      <c r="D76">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A77">
         <v>1</v>
       </c>
       <c r="B77">
         <v>76</v>
       </c>
-    </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C77">
+        <v>55</v>
+      </c>
+      <c r="D77">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A78">
         <v>1</v>
       </c>
       <c r="B78">
         <v>77</v>
       </c>
-    </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C78">
+        <v>52</v>
+      </c>
+      <c r="D78">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A79">
         <v>1</v>
       </c>
       <c r="B79">
         <v>78</v>
       </c>
-    </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C79">
+        <v>56</v>
+      </c>
+      <c r="D79">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A80">
         <v>1</v>
       </c>
       <c r="B80">
         <v>79</v>
       </c>
-    </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C80">
+        <v>28</v>
+      </c>
+      <c r="D80">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A81">
         <v>1</v>
       </c>
       <c r="B81">
         <v>80</v>
       </c>
-    </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C81">
+        <v>67</v>
+      </c>
+      <c r="D81">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A82">
         <v>1</v>
       </c>
       <c r="B82">
         <v>81</v>
       </c>
-    </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C82">
+        <v>27</v>
+      </c>
+      <c r="D82">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A83">
         <v>1</v>
       </c>
       <c r="B83">
         <v>82</v>
       </c>
-    </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C83">
+        <v>12</v>
+      </c>
+      <c r="D83">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A84">
         <v>1</v>
       </c>
       <c r="B84">
         <v>83</v>
       </c>
-    </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C84">
+        <v>39</v>
+      </c>
+      <c r="D84">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A85">
         <v>1</v>
       </c>
       <c r="B85">
         <v>84</v>
       </c>
-    </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C85">
+        <v>59</v>
+      </c>
+      <c r="D85">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A86">
         <v>1</v>
       </c>
       <c r="B86">
         <v>85</v>
       </c>
-    </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C86">
+        <v>11</v>
+      </c>
+      <c r="D86">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A87">
         <v>1</v>
       </c>
       <c r="B87">
         <v>86</v>
       </c>
-    </row>
-    <row r="88" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C87">
+        <v>1</v>
+      </c>
+      <c r="D87">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A88">
         <v>1</v>
       </c>
       <c r="B88">
         <v>87</v>
       </c>
-    </row>
-    <row r="89" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C88">
+        <v>35</v>
+      </c>
+      <c r="D88">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A89">
         <v>1</v>
       </c>
       <c r="B89">
         <v>88</v>
       </c>
-    </row>
-    <row r="90" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C89">
+        <v>37</v>
+      </c>
+      <c r="D89">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A90">
         <v>1</v>
       </c>
       <c r="B90">
         <v>89</v>
       </c>
-    </row>
-    <row r="91" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C90">
+        <v>26</v>
+      </c>
+      <c r="D90">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A91">
         <v>1</v>
       </c>
       <c r="B91">
         <v>90</v>
       </c>
-    </row>
-    <row r="92" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C91">
+        <v>47</v>
+      </c>
+      <c r="D91">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A92">
         <v>1</v>
       </c>
       <c r="B92">
         <v>91</v>
       </c>
-    </row>
-    <row r="93" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C92">
+        <v>38</v>
+      </c>
+      <c r="D92">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A93">
         <v>1</v>
       </c>
       <c r="B93">
         <v>92</v>
       </c>
-    </row>
-    <row r="94" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C93">
+        <v>57</v>
+      </c>
+      <c r="D93">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A94">
         <v>1</v>
       </c>
       <c r="B94">
         <v>93</v>
       </c>
-    </row>
-    <row r="95" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C94">
+        <v>23</v>
+      </c>
+      <c r="D94">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A95">
         <v>1</v>
       </c>
       <c r="B95">
         <v>94</v>
       </c>
-    </row>
-    <row r="96" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C95">
+        <v>21</v>
+      </c>
+      <c r="D95">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="96" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A96">
         <v>1</v>
       </c>
       <c r="B96">
         <v>95</v>
       </c>
-    </row>
-    <row r="97" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C96">
+        <v>48</v>
+      </c>
+      <c r="D96">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A97">
         <v>1</v>
       </c>
       <c r="B97">
         <v>96</v>
       </c>
-    </row>
-    <row r="98" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C97">
+        <v>60</v>
+      </c>
+      <c r="D97">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="98" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A98">
         <v>1</v>
       </c>
       <c r="B98">
         <v>97</v>
       </c>
-    </row>
-    <row r="99" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C98">
+        <v>3</v>
+      </c>
+      <c r="D98">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="99" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A99">
         <v>1</v>
       </c>
       <c r="B99">
         <v>98</v>
       </c>
-    </row>
-    <row r="100" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C99">
+        <v>66</v>
+      </c>
+      <c r="D99">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="100" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A100">
         <v>1</v>
       </c>
       <c r="B100">
         <v>99</v>
       </c>
-    </row>
-    <row r="101" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C100">
+        <v>33</v>
+      </c>
+      <c r="D100">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="101" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A101">
         <v>1</v>
       </c>
       <c r="B101">
         <v>100</v>
+      </c>
+      <c r="C101">
+        <v>10</v>
+      </c>
+      <c r="D101">
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/data_VR4.xlsx
+++ b/data_VR4.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\y0808\search-app\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6019C19-0492-4920-916E-9B7DEE06E7AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C8F96CD-EE7D-4210-AD12-536300FC5516}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3072" yWindow="1944" windowWidth="17280" windowHeight="9420" xr2:uid="{51A6361B-5262-4E40-ACE6-80335589EBEA}"/>
+    <workbookView xWindow="3072" yWindow="1944" windowWidth="17280" windowHeight="9420" activeTab="3" xr2:uid="{51A6361B-5262-4E40-ACE6-80335589EBEA}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="8">
   <si>
     <t>table</t>
     <phoneticPr fontId="1"/>
@@ -53,6 +53,10 @@
   </si>
   <si>
     <t>P-66</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>P-36</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -4721,6 +4725,12 @@
       <c r="B2">
         <v>1</v>
       </c>
+      <c r="C2">
+        <v>39</v>
+      </c>
+      <c r="D2">
+        <v>8</v>
+      </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A3">
@@ -4729,6 +4739,12 @@
       <c r="B3">
         <v>2</v>
       </c>
+      <c r="C3">
+        <v>12</v>
+      </c>
+      <c r="D3">
+        <v>19</v>
+      </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A4">
@@ -4737,6 +4753,12 @@
       <c r="B4">
         <v>3</v>
       </c>
+      <c r="C4">
+        <v>35</v>
+      </c>
+      <c r="D4">
+        <v>38</v>
+      </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A5">
@@ -4745,6 +4767,12 @@
       <c r="B5">
         <v>4</v>
       </c>
+      <c r="C5">
+        <v>2</v>
+      </c>
+      <c r="D5">
+        <v>66</v>
+      </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A6">
@@ -4753,6 +4781,12 @@
       <c r="B6">
         <v>5</v>
       </c>
+      <c r="C6">
+        <v>26</v>
+      </c>
+      <c r="D6">
+        <v>23</v>
+      </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A7">
@@ -4761,6 +4795,12 @@
       <c r="B7">
         <v>6</v>
       </c>
+      <c r="C7">
+        <v>68</v>
+      </c>
+      <c r="D7">
+        <v>12</v>
+      </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A8">
@@ -4769,6 +4809,12 @@
       <c r="B8">
         <v>7</v>
       </c>
+      <c r="C8">
+        <v>48</v>
+      </c>
+      <c r="D8">
+        <v>7</v>
+      </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A9">
@@ -4777,6 +4823,12 @@
       <c r="B9">
         <v>8</v>
       </c>
+      <c r="C9">
+        <v>41</v>
+      </c>
+      <c r="D9">
+        <v>60</v>
+      </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A10">
@@ -4785,6 +4837,12 @@
       <c r="B10">
         <v>9</v>
       </c>
+      <c r="C10">
+        <v>8</v>
+      </c>
+      <c r="D10">
+        <v>30</v>
+      </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A11">
@@ -4793,6 +4851,12 @@
       <c r="B11">
         <v>10</v>
       </c>
+      <c r="C11">
+        <v>19</v>
+      </c>
+      <c r="D11">
+        <v>57</v>
+      </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A12">
@@ -4801,6 +4865,12 @@
       <c r="B12">
         <v>11</v>
       </c>
+      <c r="C12">
+        <v>3</v>
+      </c>
+      <c r="D12">
+        <v>27</v>
+      </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A13">
@@ -4809,6 +4879,12 @@
       <c r="B13">
         <v>12</v>
       </c>
+      <c r="C13">
+        <v>24</v>
+      </c>
+      <c r="D13">
+        <v>21</v>
+      </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A14">
@@ -4817,6 +4893,12 @@
       <c r="B14">
         <v>13</v>
       </c>
+      <c r="C14">
+        <v>52</v>
+      </c>
+      <c r="D14">
+        <v>14</v>
+      </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A15">
@@ -4825,6 +4907,12 @@
       <c r="B15">
         <v>14</v>
       </c>
+      <c r="C15">
+        <v>56</v>
+      </c>
+      <c r="D15">
+        <v>6</v>
+      </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A16">
@@ -4833,685 +4921,1201 @@
       <c r="B16">
         <v>15</v>
       </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C16">
+        <v>15</v>
+      </c>
+      <c r="D16">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A17">
         <v>1</v>
       </c>
       <c r="B17">
         <v>16</v>
       </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C17">
+        <v>47</v>
+      </c>
+      <c r="D17">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A18">
         <v>1</v>
       </c>
       <c r="B18">
         <v>17</v>
       </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C18">
+        <v>23</v>
+      </c>
+      <c r="D18">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A19">
         <v>1</v>
       </c>
       <c r="B19">
         <v>18</v>
       </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C19">
+        <v>61</v>
+      </c>
+      <c r="D19">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A20">
         <v>1</v>
       </c>
       <c r="B20">
         <v>19</v>
       </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C20">
+        <v>7</v>
+      </c>
+      <c r="D20">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A21">
         <v>1</v>
       </c>
       <c r="B21">
         <v>20</v>
       </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C21">
+        <v>21</v>
+      </c>
+      <c r="D21">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A22">
         <v>1</v>
       </c>
       <c r="B22">
         <v>21</v>
       </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C22">
+        <v>27</v>
+      </c>
+      <c r="D22">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A23">
         <v>1</v>
       </c>
       <c r="B23">
         <v>22</v>
       </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C23">
+        <v>22</v>
+      </c>
+      <c r="D23">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A24">
         <v>1</v>
       </c>
       <c r="B24">
         <v>23</v>
       </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C24">
+        <v>51</v>
+      </c>
+      <c r="D24">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A25">
         <v>1</v>
       </c>
       <c r="B25">
         <v>24</v>
       </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C25">
+        <v>29</v>
+      </c>
+      <c r="D25">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A26">
         <v>1</v>
       </c>
       <c r="B26">
         <v>25</v>
       </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C26">
+        <v>45</v>
+      </c>
+      <c r="D26">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A27">
         <v>1</v>
       </c>
       <c r="B27">
         <v>26</v>
       </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C27">
+        <v>37</v>
+      </c>
+      <c r="D27">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A28">
         <v>1</v>
       </c>
       <c r="B28">
         <v>27</v>
       </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C28">
+        <v>28</v>
+      </c>
+      <c r="D28">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A29">
         <v>1</v>
       </c>
       <c r="B29">
         <v>28</v>
       </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C29">
+        <v>20</v>
+      </c>
+      <c r="D29">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A30">
         <v>1</v>
       </c>
       <c r="B30">
         <v>29</v>
       </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C30">
+        <v>3</v>
+      </c>
+      <c r="D30">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A31">
         <v>1</v>
       </c>
       <c r="B31">
         <v>30</v>
       </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C31">
+        <v>49</v>
+      </c>
+      <c r="D31">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A32">
         <v>1</v>
       </c>
       <c r="B32">
         <v>31</v>
       </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C32">
+        <v>39</v>
+      </c>
+      <c r="D32">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A33">
         <v>1</v>
       </c>
       <c r="B33">
         <v>32</v>
       </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C33">
+        <v>60</v>
+      </c>
+      <c r="D33">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A34">
         <v>1</v>
       </c>
       <c r="B34">
         <v>33</v>
       </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C34">
+        <v>30</v>
+      </c>
+      <c r="D34">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A35">
         <v>1</v>
       </c>
       <c r="B35">
         <v>34</v>
       </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C35">
+        <v>6</v>
+      </c>
+      <c r="D35">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A36">
         <v>1</v>
       </c>
       <c r="B36">
         <v>35</v>
       </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C36">
+        <v>48</v>
+      </c>
+      <c r="D36">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A37">
         <v>1</v>
       </c>
       <c r="B37">
         <v>36</v>
       </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C37">
+        <v>31</v>
+      </c>
+      <c r="D37">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A38">
         <v>1</v>
       </c>
       <c r="B38">
         <v>37</v>
       </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C38">
+        <v>33</v>
+      </c>
+      <c r="D38">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A39">
         <v>1</v>
       </c>
       <c r="B39">
         <v>38</v>
       </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C39">
+        <v>59</v>
+      </c>
+      <c r="D39">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A40">
         <v>1</v>
       </c>
       <c r="B40">
         <v>39</v>
       </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C40">
+        <v>35</v>
+      </c>
+      <c r="D40">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A41">
         <v>1</v>
       </c>
       <c r="B41">
         <v>40</v>
       </c>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C41">
+        <v>12</v>
+      </c>
+      <c r="D41">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A42">
         <v>1</v>
       </c>
       <c r="B42">
         <v>41</v>
       </c>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C42">
+        <v>16</v>
+      </c>
+      <c r="D42">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A43">
         <v>1</v>
       </c>
       <c r="B43">
         <v>42</v>
       </c>
-    </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C43">
+        <v>69</v>
+      </c>
+      <c r="D43">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A44">
         <v>1</v>
       </c>
       <c r="B44">
         <v>43</v>
       </c>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C44">
+        <v>18</v>
+      </c>
+      <c r="D44">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A45">
         <v>1</v>
       </c>
       <c r="B45">
         <v>44</v>
       </c>
-    </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C45">
+        <v>2</v>
+      </c>
+      <c r="D45">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A46">
         <v>1</v>
       </c>
       <c r="B46">
         <v>45</v>
       </c>
-    </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C46">
+        <v>52</v>
+      </c>
+      <c r="D46">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A47">
         <v>1</v>
       </c>
       <c r="B47">
         <v>46</v>
       </c>
-    </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C47">
+        <v>56</v>
+      </c>
+      <c r="D47">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A48">
         <v>1</v>
       </c>
       <c r="B48">
         <v>47</v>
       </c>
-    </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C48">
+        <v>14</v>
+      </c>
+      <c r="D48">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A49">
         <v>1</v>
       </c>
       <c r="B49">
         <v>48</v>
       </c>
-    </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C49">
+        <v>17</v>
+      </c>
+      <c r="D49">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A50">
         <v>1</v>
       </c>
       <c r="B50">
         <v>49</v>
       </c>
-    </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C50">
+        <v>11</v>
+      </c>
+      <c r="D50">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A51">
         <v>1</v>
       </c>
       <c r="B51">
         <v>50</v>
       </c>
-    </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C51">
+        <v>47</v>
+      </c>
+      <c r="D51">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A52">
         <v>1</v>
       </c>
       <c r="B52">
         <v>51</v>
       </c>
-    </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C52">
+        <v>15</v>
+      </c>
+      <c r="D52">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A53">
         <v>1</v>
       </c>
       <c r="B53">
         <v>52</v>
       </c>
-    </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C53">
+        <v>66</v>
+      </c>
+      <c r="D53">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A54">
         <v>1</v>
       </c>
       <c r="B54">
         <v>53</v>
       </c>
-    </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C54">
+        <v>45</v>
+      </c>
+      <c r="D54">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A55">
         <v>1</v>
       </c>
       <c r="B55">
         <v>54</v>
       </c>
-    </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C55">
+        <v>50</v>
+      </c>
+      <c r="D55">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A56">
         <v>1</v>
       </c>
       <c r="B56">
         <v>55</v>
       </c>
-    </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C56">
+        <v>38</v>
+      </c>
+      <c r="D56">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A57">
         <v>1</v>
       </c>
       <c r="B57">
         <v>56</v>
       </c>
-    </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C57">
+        <v>19</v>
+      </c>
+      <c r="D57">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A58">
         <v>1</v>
       </c>
       <c r="B58">
         <v>57</v>
       </c>
-    </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C58">
+        <v>27</v>
+      </c>
+      <c r="D58">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A59">
         <v>1</v>
       </c>
       <c r="B59">
         <v>58</v>
       </c>
-    </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C59">
+        <v>70</v>
+      </c>
+      <c r="D59">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A60">
         <v>1</v>
       </c>
       <c r="B60">
         <v>59</v>
       </c>
-    </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C60">
+        <v>26</v>
+      </c>
+      <c r="D60">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A61">
         <v>1</v>
       </c>
       <c r="B61">
         <v>60</v>
       </c>
-    </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C61">
+        <v>10</v>
+      </c>
+      <c r="D61" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A62">
         <v>1</v>
       </c>
       <c r="B62">
         <v>61</v>
       </c>
-    </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C62">
+        <v>4</v>
+      </c>
+      <c r="D62">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A63">
         <v>1</v>
       </c>
       <c r="B63">
         <v>62</v>
       </c>
-    </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C63">
+        <v>37</v>
+      </c>
+      <c r="D63">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A64">
         <v>1</v>
       </c>
       <c r="B64">
         <v>63</v>
       </c>
-    </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C64">
+        <v>28</v>
+      </c>
+      <c r="D64">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A65">
         <v>1</v>
       </c>
       <c r="B65">
         <v>64</v>
       </c>
-    </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C65">
+        <v>34</v>
+      </c>
+      <c r="D65">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A66">
         <v>1</v>
       </c>
       <c r="B66">
         <v>65</v>
       </c>
-    </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C66">
+        <v>51</v>
+      </c>
+      <c r="D66">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A67">
         <v>1</v>
       </c>
       <c r="B67">
         <v>66</v>
       </c>
-    </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C67">
+        <v>36</v>
+      </c>
+      <c r="D67">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A68">
         <v>1</v>
       </c>
       <c r="B68">
         <v>67</v>
       </c>
-    </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C68">
+        <v>3</v>
+      </c>
+      <c r="D68">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A69">
         <v>1</v>
       </c>
       <c r="B69">
         <v>68</v>
       </c>
-    </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C69">
+        <v>6</v>
+      </c>
+      <c r="D69">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A70">
         <v>1</v>
       </c>
       <c r="B70">
         <v>69</v>
       </c>
-    </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C70">
+        <v>8</v>
+      </c>
+      <c r="D70">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A71">
         <v>1</v>
       </c>
       <c r="B71">
         <v>70</v>
       </c>
-    </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C71">
+        <v>21</v>
+      </c>
+      <c r="D71">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A72">
         <v>1</v>
       </c>
       <c r="B72">
         <v>71</v>
       </c>
-    </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C72">
+        <v>52</v>
+      </c>
+      <c r="D72">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A73">
         <v>1</v>
       </c>
       <c r="B73">
         <v>72</v>
       </c>
-    </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C73">
+        <v>67</v>
+      </c>
+      <c r="D73">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A74">
         <v>1</v>
       </c>
       <c r="B74">
         <v>73</v>
       </c>
-    </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C74">
+        <v>48</v>
+      </c>
+      <c r="D74">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A75">
         <v>1</v>
       </c>
       <c r="B75">
         <v>74</v>
       </c>
-    </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C75">
+        <v>20</v>
+      </c>
+      <c r="D75">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A76">
         <v>1</v>
       </c>
       <c r="B76">
         <v>75</v>
       </c>
-    </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C76">
+        <v>7</v>
+      </c>
+      <c r="D76">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A77">
         <v>1</v>
       </c>
       <c r="B77">
         <v>76</v>
       </c>
-    </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C77">
+        <v>54</v>
+      </c>
+      <c r="D77">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A78">
         <v>1</v>
       </c>
       <c r="B78">
         <v>77</v>
       </c>
-    </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C78">
+        <v>16</v>
+      </c>
+      <c r="D78">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A79">
         <v>1</v>
       </c>
       <c r="B79">
         <v>78</v>
       </c>
-    </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C79">
+        <v>59</v>
+      </c>
+      <c r="D79">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A80">
         <v>1</v>
       </c>
       <c r="B80">
         <v>79</v>
       </c>
-    </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C80">
+        <v>39</v>
+      </c>
+      <c r="D80">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A81">
         <v>1</v>
       </c>
       <c r="B81">
         <v>80</v>
       </c>
-    </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C81">
+        <v>63</v>
+      </c>
+      <c r="D81">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A82">
         <v>1</v>
       </c>
       <c r="B82">
         <v>81</v>
       </c>
-    </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C82">
+        <v>38</v>
+      </c>
+      <c r="D82">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A83">
         <v>1</v>
       </c>
       <c r="B83">
         <v>82</v>
       </c>
-    </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C83">
+        <v>50</v>
+      </c>
+      <c r="D83">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A84">
         <v>1</v>
       </c>
       <c r="B84">
         <v>83</v>
       </c>
-    </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C84">
+        <v>33</v>
+      </c>
+      <c r="D84">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A85">
         <v>1</v>
       </c>
       <c r="B85">
         <v>84</v>
       </c>
-    </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C85">
+        <v>43</v>
+      </c>
+      <c r="D85">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A86">
         <v>1</v>
       </c>
       <c r="B86">
         <v>85</v>
       </c>
-    </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C86">
+        <v>14</v>
+      </c>
+      <c r="D86">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A87">
         <v>1</v>
       </c>
       <c r="B87">
         <v>86</v>
       </c>
-    </row>
-    <row r="88" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C87">
+        <v>53</v>
+      </c>
+      <c r="D87">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A88">
         <v>1</v>
       </c>
       <c r="B88">
         <v>87</v>
       </c>
-    </row>
-    <row r="89" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C88">
+        <v>23</v>
+      </c>
+      <c r="D88">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A89">
         <v>1</v>
       </c>
       <c r="B89">
         <v>88</v>
       </c>
-    </row>
-    <row r="90" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C89">
+        <v>34</v>
+      </c>
+      <c r="D89">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A90">
         <v>1</v>
       </c>
       <c r="B90">
         <v>89</v>
       </c>
-    </row>
-    <row r="91" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C90">
+        <v>30</v>
+      </c>
+      <c r="D90">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A91">
         <v>1</v>
       </c>
       <c r="B91">
         <v>90</v>
       </c>
-    </row>
-    <row r="92" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C91">
+        <v>60</v>
+      </c>
+      <c r="D91">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A92">
         <v>1</v>
       </c>
       <c r="B92">
         <v>91</v>
       </c>
-    </row>
-    <row r="93" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C92">
+        <v>11</v>
+      </c>
+      <c r="D92">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A93">
         <v>1</v>
       </c>
       <c r="B93">
         <v>92</v>
       </c>
-    </row>
-    <row r="94" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C93">
+        <v>65</v>
+      </c>
+      <c r="D93">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A94">
         <v>1</v>
       </c>
       <c r="B94">
         <v>93</v>
       </c>
-    </row>
-    <row r="95" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C94">
+        <v>45</v>
+      </c>
+      <c r="D94">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A95">
         <v>1</v>
       </c>
       <c r="B95">
         <v>94</v>
       </c>
-    </row>
-    <row r="96" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C95">
+        <v>10</v>
+      </c>
+      <c r="D95">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="96" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A96">
         <v>1</v>
       </c>
       <c r="B96">
         <v>95</v>
       </c>
-    </row>
-    <row r="97" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C96">
+        <v>4</v>
+      </c>
+      <c r="D96">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A97">
         <v>1</v>
       </c>
       <c r="B97">
         <v>96</v>
       </c>
-    </row>
-    <row r="98" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C97">
+        <v>54</v>
+      </c>
+      <c r="D97">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="98" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A98">
         <v>1</v>
       </c>
       <c r="B98">
         <v>97</v>
       </c>
-    </row>
-    <row r="99" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C98">
+        <v>51</v>
+      </c>
+      <c r="D98">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="99" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A99">
         <v>1</v>
       </c>
       <c r="B99">
         <v>98</v>
       </c>
-    </row>
-    <row r="100" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C99">
+        <v>32</v>
+      </c>
+      <c r="D99">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="100" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A100">
         <v>1</v>
       </c>
       <c r="B100">
         <v>99</v>
       </c>
-    </row>
-    <row r="101" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C100">
+        <v>18</v>
+      </c>
+      <c r="D100">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="101" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A101">
         <v>1</v>
       </c>
       <c r="B101">
         <v>100</v>
+      </c>
+      <c r="C101">
+        <v>22</v>
+      </c>
+      <c r="D101">
+        <v>20</v>
       </c>
     </row>
   </sheetData>

--- a/data_VR4.xlsx
+++ b/data_VR4.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\y0808\search-app\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C8F96CD-EE7D-4210-AD12-536300FC5516}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B67E9683-9099-4865-B556-9DDDEE184DD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3072" yWindow="1944" windowWidth="17280" windowHeight="9420" activeTab="3" xr2:uid="{51A6361B-5262-4E40-ACE6-80335589EBEA}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" activeTab="5" xr2:uid="{51A6361B-5262-4E40-ACE6-80335589EBEA}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="10">
   <si>
     <t>table</t>
     <phoneticPr fontId="1"/>
@@ -61,6 +61,14 @@
   </si>
   <si>
     <t>P-36</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>P-66</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>P-24</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -6151,6 +6159,12 @@
       <c r="B2">
         <v>1</v>
       </c>
+      <c r="C2">
+        <v>15</v>
+      </c>
+      <c r="D2">
+        <v>11</v>
+      </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A3">
@@ -6159,6 +6173,12 @@
       <c r="B3">
         <v>2</v>
       </c>
+      <c r="C3">
+        <v>34</v>
+      </c>
+      <c r="D3">
+        <v>56</v>
+      </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A4">
@@ -6167,6 +6187,12 @@
       <c r="B4">
         <v>3</v>
       </c>
+      <c r="C4">
+        <v>52</v>
+      </c>
+      <c r="D4">
+        <v>26</v>
+      </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A5">
@@ -6175,6 +6201,12 @@
       <c r="B5">
         <v>4</v>
       </c>
+      <c r="C5">
+        <v>19</v>
+      </c>
+      <c r="D5">
+        <v>64</v>
+      </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A6">
@@ -6183,6 +6215,12 @@
       <c r="B6">
         <v>5</v>
       </c>
+      <c r="C6">
+        <v>26</v>
+      </c>
+      <c r="D6">
+        <v>16</v>
+      </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A7">
@@ -6191,6 +6229,12 @@
       <c r="B7">
         <v>6</v>
       </c>
+      <c r="C7">
+        <v>13</v>
+      </c>
+      <c r="D7">
+        <v>20</v>
+      </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A8">
@@ -6199,6 +6243,12 @@
       <c r="B8">
         <v>7</v>
       </c>
+      <c r="C8">
+        <v>35</v>
+      </c>
+      <c r="D8">
+        <v>8</v>
+      </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A9">
@@ -6207,6 +6257,12 @@
       <c r="B9">
         <v>8</v>
       </c>
+      <c r="C9">
+        <v>22</v>
+      </c>
+      <c r="D9">
+        <v>22</v>
+      </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A10">
@@ -6215,6 +6271,12 @@
       <c r="B10">
         <v>9</v>
       </c>
+      <c r="C10">
+        <v>4</v>
+      </c>
+      <c r="D10">
+        <v>39</v>
+      </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A11">
@@ -6223,6 +6285,12 @@
       <c r="B11">
         <v>10</v>
       </c>
+      <c r="C11">
+        <v>20</v>
+      </c>
+      <c r="D11">
+        <v>32</v>
+      </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A12">
@@ -6231,6 +6299,12 @@
       <c r="B12">
         <v>11</v>
       </c>
+      <c r="C12">
+        <v>14</v>
+      </c>
+      <c r="D12">
+        <v>7</v>
+      </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A13">
@@ -6239,6 +6313,12 @@
       <c r="B13">
         <v>12</v>
       </c>
+      <c r="C13">
+        <v>63</v>
+      </c>
+      <c r="D13">
+        <v>2</v>
+      </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A14">
@@ -6247,6 +6327,12 @@
       <c r="B14">
         <v>13</v>
       </c>
+      <c r="C14">
+        <v>51</v>
+      </c>
+      <c r="D14">
+        <v>33</v>
+      </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A15">
@@ -6255,6 +6341,12 @@
       <c r="B15">
         <v>14</v>
       </c>
+      <c r="C15">
+        <v>21</v>
+      </c>
+      <c r="D15">
+        <v>41</v>
+      </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A16">
@@ -6263,685 +6355,1201 @@
       <c r="B16">
         <v>15</v>
       </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C16">
+        <v>28</v>
+      </c>
+      <c r="D16">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A17">
         <v>1</v>
       </c>
       <c r="B17">
         <v>16</v>
       </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C17">
+        <v>37</v>
+      </c>
+      <c r="D17">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A18">
         <v>1</v>
       </c>
       <c r="B18">
         <v>17</v>
       </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C18">
+        <v>7</v>
+      </c>
+      <c r="D18">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A19">
         <v>1</v>
       </c>
       <c r="B19">
         <v>18</v>
       </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C19">
+        <v>64</v>
+      </c>
+      <c r="D19">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A20">
         <v>1</v>
       </c>
       <c r="B20">
         <v>19</v>
       </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C20">
+        <v>39</v>
+      </c>
+      <c r="D20">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A21">
         <v>1</v>
       </c>
       <c r="B21">
         <v>20</v>
       </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C21">
+        <v>6</v>
+      </c>
+      <c r="D21">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A22">
         <v>1</v>
       </c>
       <c r="B22">
         <v>21</v>
       </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C22">
+        <v>23</v>
+      </c>
+      <c r="D22">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A23">
         <v>1</v>
       </c>
       <c r="B23">
         <v>22</v>
       </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C23">
+        <v>60</v>
+      </c>
+      <c r="D23">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A24">
         <v>1</v>
       </c>
       <c r="B24">
         <v>23</v>
       </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C24">
+        <v>3</v>
+      </c>
+      <c r="D24">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A25">
         <v>1</v>
       </c>
       <c r="B25">
         <v>24</v>
       </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C25">
+        <v>56</v>
+      </c>
+      <c r="D25">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A26">
         <v>1</v>
       </c>
       <c r="B26">
         <v>25</v>
       </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C26">
+        <v>18</v>
+      </c>
+      <c r="D26">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A27">
         <v>1</v>
       </c>
       <c r="B27">
         <v>26</v>
       </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C27">
+        <v>24</v>
+      </c>
+      <c r="D27">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A28">
         <v>1</v>
       </c>
       <c r="B28">
         <v>27</v>
       </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C28">
+        <v>16</v>
+      </c>
+      <c r="D28">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A29">
         <v>1</v>
       </c>
       <c r="B29">
         <v>28</v>
       </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C29">
+        <v>54</v>
+      </c>
+      <c r="D29">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A30">
         <v>1</v>
       </c>
       <c r="B30">
         <v>29</v>
       </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C30">
+        <v>8</v>
+      </c>
+      <c r="D30">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A31">
         <v>1</v>
       </c>
       <c r="B31">
         <v>30</v>
       </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C31">
+        <v>47</v>
+      </c>
+      <c r="D31">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A32">
         <v>1</v>
       </c>
       <c r="B32">
         <v>31</v>
       </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C32">
+        <v>27</v>
+      </c>
+      <c r="D32">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A33">
         <v>1</v>
       </c>
       <c r="B33">
         <v>32</v>
       </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C33">
+        <v>58</v>
+      </c>
+      <c r="D33">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A34">
         <v>1</v>
       </c>
       <c r="B34">
         <v>33</v>
       </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C34">
+        <v>14</v>
+      </c>
+      <c r="D34">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A35">
         <v>1</v>
       </c>
       <c r="B35">
         <v>34</v>
       </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C35">
+        <v>34</v>
+      </c>
+      <c r="D35">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A36">
         <v>1</v>
       </c>
       <c r="B36">
         <v>35</v>
       </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C36">
+        <v>4</v>
+      </c>
+      <c r="D36">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A37">
         <v>1</v>
       </c>
       <c r="B37">
         <v>36</v>
       </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C37">
+        <v>50</v>
+      </c>
+      <c r="D37">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A38">
         <v>1</v>
       </c>
       <c r="B38">
         <v>37</v>
       </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C38">
+        <v>11</v>
+      </c>
+      <c r="D38">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A39">
         <v>1</v>
       </c>
       <c r="B39">
         <v>38</v>
       </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C39">
+        <v>68</v>
+      </c>
+      <c r="D39">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A40">
         <v>1</v>
       </c>
       <c r="B40">
         <v>39</v>
       </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C40">
+        <v>35</v>
+      </c>
+      <c r="D40">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A41">
         <v>1</v>
       </c>
       <c r="B41">
         <v>40</v>
       </c>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C41">
+        <v>2</v>
+      </c>
+      <c r="D41">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A42">
         <v>1</v>
       </c>
       <c r="B42">
         <v>41</v>
       </c>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C42">
+        <v>27</v>
+      </c>
+      <c r="D42">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A43">
         <v>1</v>
       </c>
       <c r="B43">
         <v>42</v>
       </c>
-    </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C43">
+        <v>10</v>
+      </c>
+      <c r="D43">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A44">
         <v>1</v>
       </c>
       <c r="B44">
         <v>43</v>
       </c>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C44">
+        <v>33</v>
+      </c>
+      <c r="D44">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A45">
         <v>1</v>
       </c>
       <c r="B45">
         <v>44</v>
       </c>
-    </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C45">
+        <v>44</v>
+      </c>
+      <c r="D45">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A46">
         <v>1</v>
       </c>
       <c r="B46">
         <v>45</v>
       </c>
-    </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C46">
+        <v>30</v>
+      </c>
+      <c r="D46">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A47">
         <v>1</v>
       </c>
       <c r="B47">
         <v>46</v>
       </c>
-    </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C47">
+        <v>19</v>
+      </c>
+      <c r="D47">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A48">
         <v>1</v>
       </c>
       <c r="B48">
         <v>47</v>
       </c>
-    </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C48">
+        <v>26</v>
+      </c>
+      <c r="D48">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A49">
         <v>1</v>
       </c>
       <c r="B49">
         <v>48</v>
       </c>
-    </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C49">
+        <v>54</v>
+      </c>
+      <c r="D49">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A50">
         <v>1</v>
       </c>
       <c r="B50">
         <v>49</v>
       </c>
-    </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C50">
+        <v>48</v>
+      </c>
+      <c r="D50">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A51">
         <v>1</v>
       </c>
       <c r="B51">
         <v>50</v>
       </c>
-    </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C51">
+        <v>70</v>
+      </c>
+      <c r="D51">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A52">
         <v>1</v>
       </c>
       <c r="B52">
         <v>51</v>
       </c>
-    </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C52">
+        <v>28</v>
+      </c>
+      <c r="D52">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A53">
         <v>1</v>
       </c>
       <c r="B53">
         <v>52</v>
       </c>
-    </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C53">
+        <v>12</v>
+      </c>
+      <c r="D53">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A54">
         <v>1</v>
       </c>
       <c r="B54">
         <v>53</v>
       </c>
-    </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C54">
+        <v>15</v>
+      </c>
+      <c r="D54">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A55">
         <v>1</v>
       </c>
       <c r="B55">
         <v>54</v>
       </c>
-    </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C55">
+        <v>55</v>
+      </c>
+      <c r="D55">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A56">
         <v>1</v>
       </c>
       <c r="B56">
         <v>55</v>
       </c>
-    </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C56">
+        <v>38</v>
+      </c>
+      <c r="D56">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A57">
         <v>1</v>
       </c>
       <c r="B57">
         <v>56</v>
       </c>
-    </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C57">
+        <v>22</v>
+      </c>
+      <c r="D57">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A58">
         <v>1</v>
       </c>
       <c r="B58">
         <v>57</v>
       </c>
-    </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C58">
+        <v>16</v>
+      </c>
+      <c r="D58">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A59">
         <v>1</v>
       </c>
       <c r="B59">
         <v>58</v>
       </c>
-    </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C59">
+        <v>21</v>
+      </c>
+      <c r="D59">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A60">
         <v>1</v>
       </c>
       <c r="B60">
         <v>59</v>
       </c>
-    </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C60">
+        <v>7</v>
+      </c>
+      <c r="D60">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A61">
         <v>1</v>
       </c>
       <c r="B61">
         <v>60</v>
       </c>
-    </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C61">
+        <v>59</v>
+      </c>
+      <c r="D61">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A62">
         <v>1</v>
       </c>
       <c r="B62">
         <v>61</v>
       </c>
-    </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C62">
+        <v>45</v>
+      </c>
+      <c r="D62">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A63">
         <v>1</v>
       </c>
       <c r="B63">
         <v>62</v>
       </c>
-    </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C63">
+        <v>66</v>
+      </c>
+      <c r="D63">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A64">
         <v>1</v>
       </c>
       <c r="B64">
         <v>63</v>
       </c>
-    </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C64">
+        <v>3</v>
+      </c>
+      <c r="D64">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A65">
         <v>1</v>
       </c>
       <c r="B65">
         <v>64</v>
       </c>
-    </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C65">
+        <v>43</v>
+      </c>
+      <c r="D65">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A66">
         <v>1</v>
       </c>
       <c r="B66">
         <v>65</v>
       </c>
-    </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C66">
+        <v>18</v>
+      </c>
+      <c r="D66">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A67">
         <v>1</v>
       </c>
       <c r="B67">
         <v>66</v>
       </c>
-    </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C67">
+        <v>20</v>
+      </c>
+      <c r="D67">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A68">
         <v>1</v>
       </c>
       <c r="B68">
         <v>67</v>
       </c>
-    </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C68">
+        <v>8</v>
+      </c>
+      <c r="D68">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A69">
         <v>1</v>
       </c>
       <c r="B69">
         <v>68</v>
       </c>
-    </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C69">
+        <v>67</v>
+      </c>
+      <c r="D69" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A70">
         <v>1</v>
       </c>
       <c r="B70">
         <v>69</v>
       </c>
-    </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C70">
+        <v>52</v>
+      </c>
+      <c r="D70">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A71">
         <v>1</v>
       </c>
       <c r="B71">
         <v>70</v>
       </c>
-    </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C71">
+        <v>50</v>
+      </c>
+      <c r="D71">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A72">
         <v>1</v>
       </c>
       <c r="B72">
         <v>71</v>
       </c>
-    </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C72">
+        <v>14</v>
+      </c>
+      <c r="D72">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A73">
         <v>1</v>
       </c>
       <c r="B73">
         <v>72</v>
       </c>
-    </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C73">
+        <v>12</v>
+      </c>
+      <c r="D73">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A74">
         <v>1</v>
       </c>
       <c r="B74">
         <v>73</v>
       </c>
-    </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C74">
+        <v>23</v>
+      </c>
+      <c r="D74">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A75">
         <v>1</v>
       </c>
       <c r="B75">
         <v>74</v>
       </c>
-    </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C75">
+        <v>42</v>
+      </c>
+      <c r="D75">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A76">
         <v>1</v>
       </c>
       <c r="B76">
         <v>75</v>
       </c>
-    </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C76">
+        <v>4</v>
+      </c>
+      <c r="D76">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A77">
         <v>1</v>
       </c>
       <c r="B77">
         <v>76</v>
       </c>
-    </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C77">
+        <v>41</v>
+      </c>
+      <c r="D77">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A78">
         <v>1</v>
       </c>
       <c r="B78">
         <v>77</v>
       </c>
-    </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C78">
+        <v>51</v>
+      </c>
+      <c r="D78">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A79">
         <v>1</v>
       </c>
       <c r="B79">
         <v>78</v>
       </c>
-    </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C79">
+        <v>6</v>
+      </c>
+      <c r="D79">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A80">
         <v>1</v>
       </c>
       <c r="B80">
         <v>79</v>
       </c>
-    </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C80">
+        <v>39</v>
+      </c>
+      <c r="D80">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A81">
         <v>1</v>
       </c>
       <c r="B81">
         <v>80</v>
       </c>
-    </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C81">
+        <v>61</v>
+      </c>
+      <c r="D81">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A82">
         <v>1</v>
       </c>
       <c r="B82">
         <v>81</v>
       </c>
-    </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C82">
+        <v>27</v>
+      </c>
+      <c r="D82">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A83">
         <v>1</v>
       </c>
       <c r="B83">
         <v>82</v>
       </c>
-    </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C83">
+        <v>47</v>
+      </c>
+      <c r="D83">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A84">
         <v>1</v>
       </c>
       <c r="B84">
         <v>83</v>
       </c>
-    </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C84">
+        <v>33</v>
+      </c>
+      <c r="D84">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A85">
         <v>1</v>
       </c>
       <c r="B85">
         <v>84</v>
       </c>
-    </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C85">
+        <v>37</v>
+      </c>
+      <c r="D85">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A86">
         <v>1</v>
       </c>
       <c r="B86">
         <v>85</v>
       </c>
-    </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C86">
+        <v>11</v>
+      </c>
+      <c r="D86">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A87">
         <v>1</v>
       </c>
       <c r="B87">
         <v>86</v>
       </c>
-    </row>
-    <row r="88" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C87">
+        <v>57</v>
+      </c>
+      <c r="D87">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A88">
         <v>1</v>
       </c>
       <c r="B88">
         <v>87</v>
       </c>
-    </row>
-    <row r="89" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C88">
+        <v>48</v>
+      </c>
+      <c r="D88">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A89">
         <v>1</v>
       </c>
       <c r="B89">
         <v>88</v>
       </c>
-    </row>
-    <row r="90" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C89">
+        <v>10</v>
+      </c>
+      <c r="D89">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A90">
         <v>1</v>
       </c>
       <c r="B90">
         <v>89</v>
       </c>
-    </row>
-    <row r="91" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C90">
+        <v>30</v>
+      </c>
+      <c r="D90">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A91">
         <v>1</v>
       </c>
       <c r="B91">
         <v>90</v>
       </c>
-    </row>
-    <row r="92" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C91">
+        <v>2</v>
+      </c>
+      <c r="D91">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A92">
         <v>1</v>
       </c>
       <c r="B92">
         <v>91</v>
       </c>
-    </row>
-    <row r="93" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C92">
+        <v>38</v>
+      </c>
+      <c r="D92">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A93">
         <v>1</v>
       </c>
       <c r="B93">
         <v>92</v>
       </c>
-    </row>
-    <row r="94" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C93">
+        <v>46</v>
+      </c>
+      <c r="D93">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A94">
         <v>1</v>
       </c>
       <c r="B94">
         <v>93</v>
       </c>
-    </row>
-    <row r="95" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C94">
+        <v>16</v>
+      </c>
+      <c r="D94">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A95">
         <v>1</v>
       </c>
       <c r="B95">
         <v>94</v>
       </c>
-    </row>
-    <row r="96" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C95">
+        <v>56</v>
+      </c>
+      <c r="D95">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="96" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A96">
         <v>1</v>
       </c>
       <c r="B96">
         <v>95</v>
       </c>
-    </row>
-    <row r="97" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C96">
+        <v>45</v>
+      </c>
+      <c r="D96">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A97">
         <v>1</v>
       </c>
       <c r="B97">
         <v>96</v>
       </c>
-    </row>
-    <row r="98" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C97">
+        <v>41</v>
+      </c>
+      <c r="D97">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="98" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A98">
         <v>1</v>
       </c>
       <c r="B98">
         <v>97</v>
       </c>
-    </row>
-    <row r="99" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C98">
+        <v>8</v>
+      </c>
+      <c r="D98">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="99" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A99">
         <v>1</v>
       </c>
       <c r="B99">
         <v>98</v>
       </c>
-    </row>
-    <row r="100" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C99">
+        <v>62</v>
+      </c>
+      <c r="D99">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="100" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A100">
         <v>1</v>
       </c>
       <c r="B100">
         <v>99</v>
       </c>
-    </row>
-    <row r="101" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C100">
+        <v>23</v>
+      </c>
+      <c r="D100">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="101" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A101">
         <v>1</v>
       </c>
       <c r="B101">
         <v>100</v>
+      </c>
+      <c r="C101">
+        <v>43</v>
+      </c>
+      <c r="D101">
+        <v>60</v>
       </c>
     </row>
   </sheetData>
@@ -6977,6 +7585,12 @@
       <c r="B2">
         <v>1</v>
       </c>
+      <c r="C2">
+        <v>14</v>
+      </c>
+      <c r="D2">
+        <v>7</v>
+      </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A3">
@@ -6985,6 +7599,12 @@
       <c r="B3">
         <v>2</v>
       </c>
+      <c r="C3">
+        <v>37</v>
+      </c>
+      <c r="D3">
+        <v>41</v>
+      </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A4">
@@ -6993,6 +7613,12 @@
       <c r="B4">
         <v>3</v>
       </c>
+      <c r="C4">
+        <v>26</v>
+      </c>
+      <c r="D4">
+        <v>4</v>
+      </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A5">
@@ -7001,6 +7627,12 @@
       <c r="B5">
         <v>4</v>
       </c>
+      <c r="C5">
+        <v>6</v>
+      </c>
+      <c r="D5">
+        <v>21</v>
+      </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A6">
@@ -7009,6 +7641,12 @@
       <c r="B6">
         <v>5</v>
       </c>
+      <c r="C6">
+        <v>51</v>
+      </c>
+      <c r="D6">
+        <v>15</v>
+      </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A7">
@@ -7017,6 +7655,12 @@
       <c r="B7">
         <v>6</v>
       </c>
+      <c r="C7">
+        <v>9</v>
+      </c>
+      <c r="D7">
+        <v>68</v>
+      </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A8">
@@ -7025,6 +7669,12 @@
       <c r="B8">
         <v>7</v>
       </c>
+      <c r="C8">
+        <v>11</v>
+      </c>
+      <c r="D8">
+        <v>35</v>
+      </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A9">
@@ -7033,6 +7683,12 @@
       <c r="B9">
         <v>8</v>
       </c>
+      <c r="C9">
+        <v>54</v>
+      </c>
+      <c r="D9">
+        <v>60</v>
+      </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A10">
@@ -7041,6 +7697,12 @@
       <c r="B10">
         <v>9</v>
       </c>
+      <c r="C10">
+        <v>23</v>
+      </c>
+      <c r="D10">
+        <v>3</v>
+      </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A11">
@@ -7049,6 +7711,12 @@
       <c r="B11">
         <v>10</v>
       </c>
+      <c r="C11">
+        <v>34</v>
+      </c>
+      <c r="D11">
+        <v>2</v>
+      </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A12">
@@ -7057,6 +7725,12 @@
       <c r="B12">
         <v>11</v>
       </c>
+      <c r="C12">
+        <v>15</v>
+      </c>
+      <c r="D12">
+        <v>30</v>
+      </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A13">
@@ -7065,6 +7739,12 @@
       <c r="B13">
         <v>12</v>
       </c>
+      <c r="C13">
+        <v>67</v>
+      </c>
+      <c r="D13">
+        <v>54</v>
+      </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A14">
@@ -7073,6 +7753,12 @@
       <c r="B14">
         <v>13</v>
       </c>
+      <c r="C14">
+        <v>48</v>
+      </c>
+      <c r="D14">
+        <v>33</v>
+      </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A15">
@@ -7081,6 +7767,12 @@
       <c r="B15">
         <v>14</v>
       </c>
+      <c r="C15">
+        <v>20</v>
+      </c>
+      <c r="D15">
+        <v>32</v>
+      </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A16">
@@ -7089,685 +7781,1201 @@
       <c r="B16">
         <v>15</v>
       </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C16">
+        <v>7</v>
+      </c>
+      <c r="D16">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A17">
         <v>1</v>
       </c>
       <c r="B17">
         <v>16</v>
       </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C17">
+        <v>10</v>
+      </c>
+      <c r="D17">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A18">
         <v>1</v>
       </c>
       <c r="B18">
         <v>17</v>
       </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C18">
+        <v>45</v>
+      </c>
+      <c r="D18">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A19">
         <v>1</v>
       </c>
       <c r="B19">
         <v>18</v>
       </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C19">
+        <v>17</v>
+      </c>
+      <c r="D19">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A20">
         <v>1</v>
       </c>
       <c r="B20">
         <v>19</v>
       </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C20">
+        <v>3</v>
+      </c>
+      <c r="D20">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A21">
         <v>1</v>
       </c>
       <c r="B21">
         <v>20</v>
       </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C21">
+        <v>56</v>
+      </c>
+      <c r="D21">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A22">
         <v>1</v>
       </c>
       <c r="B22">
         <v>21</v>
       </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C22">
+        <v>28</v>
+      </c>
+      <c r="D22">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A23">
         <v>1</v>
       </c>
       <c r="B23">
         <v>22</v>
       </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C23">
+        <v>47</v>
+      </c>
+      <c r="D23">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A24">
         <v>1</v>
       </c>
       <c r="B24">
         <v>23</v>
       </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C24">
+        <v>27</v>
+      </c>
+      <c r="D24">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A25">
         <v>1</v>
       </c>
       <c r="B25">
         <v>24</v>
       </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C25">
+        <v>21</v>
+      </c>
+      <c r="D25">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A26">
         <v>1</v>
       </c>
       <c r="B26">
         <v>25</v>
       </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C26">
+        <v>16</v>
+      </c>
+      <c r="D26">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A27">
         <v>1</v>
       </c>
       <c r="B27">
         <v>26</v>
       </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C27">
+        <v>66</v>
+      </c>
+      <c r="D27">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A28">
         <v>1</v>
       </c>
       <c r="B28">
         <v>27</v>
       </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C28">
+        <v>39</v>
+      </c>
+      <c r="D28">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A29">
         <v>1</v>
       </c>
       <c r="B29">
         <v>28</v>
       </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C29">
+        <v>43</v>
+      </c>
+      <c r="D29">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A30">
         <v>1</v>
       </c>
       <c r="B30">
         <v>29</v>
       </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C30">
+        <v>30</v>
+      </c>
+      <c r="D30">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A31">
         <v>1</v>
       </c>
       <c r="B31">
         <v>30</v>
       </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C31">
+        <v>22</v>
+      </c>
+      <c r="D31">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A32">
         <v>1</v>
       </c>
       <c r="B32">
         <v>31</v>
       </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C32">
+        <v>52</v>
+      </c>
+      <c r="D32">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A33">
         <v>1</v>
       </c>
       <c r="B33">
         <v>32</v>
       </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C33">
+        <v>13</v>
+      </c>
+      <c r="D33">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A34">
         <v>1</v>
       </c>
       <c r="B34">
         <v>33</v>
       </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C34">
+        <v>18</v>
+      </c>
+      <c r="D34">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A35">
         <v>1</v>
       </c>
       <c r="B35">
         <v>34</v>
       </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C35">
+        <v>60</v>
+      </c>
+      <c r="D35">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A36">
         <v>1</v>
       </c>
       <c r="B36">
         <v>35</v>
       </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C36">
+        <v>35</v>
+      </c>
+      <c r="D36">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A37">
         <v>1</v>
       </c>
       <c r="B37">
         <v>36</v>
       </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C37">
+        <v>20</v>
+      </c>
+      <c r="D37">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A38">
         <v>1</v>
       </c>
       <c r="B38">
         <v>37</v>
       </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C38">
+        <v>38</v>
+      </c>
+      <c r="D38">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A39">
         <v>1</v>
       </c>
       <c r="B39">
         <v>38</v>
       </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C39">
+        <v>2</v>
+      </c>
+      <c r="D39">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A40">
         <v>1</v>
       </c>
       <c r="B40">
         <v>39</v>
       </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C40">
+        <v>48</v>
+      </c>
+      <c r="D40">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A41">
         <v>1</v>
       </c>
       <c r="B41">
         <v>40</v>
       </c>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C41">
+        <v>69</v>
+      </c>
+      <c r="D41">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A42">
         <v>1</v>
       </c>
       <c r="B42">
         <v>41</v>
       </c>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C42">
+        <v>8</v>
+      </c>
+      <c r="D42">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A43">
         <v>1</v>
       </c>
       <c r="B43">
         <v>42</v>
       </c>
-    </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C43">
+        <v>59</v>
+      </c>
+      <c r="D43">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A44">
         <v>1</v>
       </c>
       <c r="B44">
         <v>43</v>
       </c>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C44">
+        <v>26</v>
+      </c>
+      <c r="D44">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A45">
         <v>1</v>
       </c>
       <c r="B45">
         <v>44</v>
       </c>
-    </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C45">
+        <v>41</v>
+      </c>
+      <c r="D45">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A46">
         <v>1</v>
       </c>
       <c r="B46">
         <v>45</v>
       </c>
-    </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C46">
+        <v>14</v>
+      </c>
+      <c r="D46">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A47">
         <v>1</v>
       </c>
       <c r="B47">
         <v>46</v>
       </c>
-    </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C47">
+        <v>65</v>
+      </c>
+      <c r="D47" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A48">
         <v>1</v>
       </c>
       <c r="B48">
         <v>47</v>
       </c>
-    </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C48">
+        <v>7</v>
+      </c>
+      <c r="D48">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A49">
         <v>1</v>
       </c>
       <c r="B49">
         <v>48</v>
       </c>
-    </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C49">
+        <v>50</v>
+      </c>
+      <c r="D49">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A50">
         <v>1</v>
       </c>
       <c r="B50">
         <v>49</v>
       </c>
-    </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C50">
+        <v>15</v>
+      </c>
+      <c r="D50">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A51">
         <v>1</v>
       </c>
       <c r="B51">
         <v>50</v>
       </c>
-    </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C51">
+        <v>34</v>
+      </c>
+      <c r="D51">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A52">
         <v>1</v>
       </c>
       <c r="B52">
         <v>51</v>
       </c>
-    </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C52">
+        <v>4</v>
+      </c>
+      <c r="D52">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A53">
         <v>1</v>
       </c>
       <c r="B53">
         <v>52</v>
       </c>
-    </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C53">
+        <v>12</v>
+      </c>
+      <c r="D53">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A54">
         <v>1</v>
       </c>
       <c r="B54">
         <v>53</v>
       </c>
-    </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C54">
+        <v>45</v>
+      </c>
+      <c r="D54">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A55">
         <v>1</v>
       </c>
       <c r="B55">
         <v>54</v>
       </c>
-    </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C55">
+        <v>40</v>
+      </c>
+      <c r="D55">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A56">
         <v>1</v>
       </c>
       <c r="B56">
         <v>55</v>
       </c>
-    </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C56">
+        <v>16</v>
+      </c>
+      <c r="D56">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A57">
         <v>1</v>
       </c>
       <c r="B57">
         <v>56</v>
       </c>
-    </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C57">
+        <v>6</v>
+      </c>
+      <c r="D57">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A58">
         <v>1</v>
       </c>
       <c r="B58">
         <v>57</v>
       </c>
-    </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C58">
+        <v>3</v>
+      </c>
+      <c r="D58">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A59">
         <v>1</v>
       </c>
       <c r="B59">
         <v>58</v>
       </c>
-    </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C59">
+        <v>37</v>
+      </c>
+      <c r="D59">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A60">
         <v>1</v>
       </c>
       <c r="B60">
         <v>59</v>
       </c>
-    </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C60">
+        <v>23</v>
+      </c>
+      <c r="D60">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A61">
         <v>1</v>
       </c>
       <c r="B61">
         <v>60</v>
       </c>
-    </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C61">
+        <v>70</v>
+      </c>
+      <c r="D61">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A62">
         <v>1</v>
       </c>
       <c r="B62">
         <v>61</v>
       </c>
-    </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C62">
+        <v>18</v>
+      </c>
+      <c r="D62">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A63">
         <v>1</v>
       </c>
       <c r="B63">
         <v>62</v>
       </c>
-    </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C63">
+        <v>54</v>
+      </c>
+      <c r="D63">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A64">
         <v>1</v>
       </c>
       <c r="B64">
         <v>63</v>
       </c>
-    </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C64">
+        <v>11</v>
+      </c>
+      <c r="D64">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A65">
         <v>1</v>
       </c>
       <c r="B65">
         <v>64</v>
       </c>
-    </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C65">
+        <v>24</v>
+      </c>
+      <c r="D65">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A66">
         <v>1</v>
       </c>
       <c r="B66">
         <v>65</v>
       </c>
-    </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C66">
+        <v>51</v>
+      </c>
+      <c r="D66">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A67">
         <v>1</v>
       </c>
       <c r="B67">
         <v>66</v>
       </c>
-    </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C67">
+        <v>47</v>
+      </c>
+      <c r="D67">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A68">
         <v>1</v>
       </c>
       <c r="B68">
         <v>67</v>
       </c>
-    </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C68">
+        <v>33</v>
+      </c>
+      <c r="D68">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A69">
         <v>1</v>
       </c>
       <c r="B69">
         <v>68</v>
       </c>
-    </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C69">
+        <v>61</v>
+      </c>
+      <c r="D69">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A70">
         <v>1</v>
       </c>
       <c r="B70">
         <v>69</v>
       </c>
-    </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C70">
+        <v>39</v>
+      </c>
+      <c r="D70">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A71">
         <v>1</v>
       </c>
       <c r="B71">
         <v>70</v>
       </c>
-    </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C71">
+        <v>43</v>
+      </c>
+      <c r="D71">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A72">
         <v>1</v>
       </c>
       <c r="B72">
         <v>71</v>
       </c>
-    </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C72">
+        <v>27</v>
+      </c>
+      <c r="D72">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A73">
         <v>1</v>
       </c>
       <c r="B73">
         <v>72</v>
       </c>
-    </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C73">
+        <v>55</v>
+      </c>
+      <c r="D73">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A74">
         <v>1</v>
       </c>
       <c r="B74">
         <v>73</v>
       </c>
-    </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C74">
+        <v>35</v>
+      </c>
+      <c r="D74">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A75">
         <v>1</v>
       </c>
       <c r="B75">
         <v>74</v>
       </c>
-    </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C75">
+        <v>59</v>
+      </c>
+      <c r="D75">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A76">
         <v>1</v>
       </c>
       <c r="B76">
         <v>75</v>
       </c>
-    </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C76">
+        <v>45</v>
+      </c>
+      <c r="D76">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A77">
         <v>1</v>
       </c>
       <c r="B77">
         <v>76</v>
       </c>
-    </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C77">
+        <v>21</v>
+      </c>
+      <c r="D77">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A78">
         <v>1</v>
       </c>
       <c r="B78">
         <v>77</v>
       </c>
-    </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C78">
+        <v>8</v>
+      </c>
+      <c r="D78">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A79">
         <v>1</v>
       </c>
       <c r="B79">
         <v>78</v>
       </c>
-    </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C79">
+        <v>64</v>
+      </c>
+      <c r="D79">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A80">
         <v>1</v>
       </c>
       <c r="B80">
         <v>79</v>
       </c>
-    </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C80">
+        <v>28</v>
+      </c>
+      <c r="D80">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A81">
         <v>1</v>
       </c>
       <c r="B81">
         <v>80</v>
       </c>
-    </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C81">
+        <v>56</v>
+      </c>
+      <c r="D81">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A82">
         <v>1</v>
       </c>
       <c r="B82">
         <v>81</v>
       </c>
-    </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C82">
+        <v>30</v>
+      </c>
+      <c r="D82">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A83">
         <v>1</v>
       </c>
       <c r="B83">
         <v>82</v>
       </c>
-    </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C83">
+        <v>22</v>
+      </c>
+      <c r="D83">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A84">
         <v>1</v>
       </c>
       <c r="B84">
         <v>83</v>
       </c>
-    </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C84">
+        <v>26</v>
+      </c>
+      <c r="D84">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A85">
         <v>1</v>
       </c>
       <c r="B85">
         <v>84</v>
       </c>
-    </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C85">
+        <v>58</v>
+      </c>
+      <c r="D85">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A86">
         <v>1</v>
       </c>
       <c r="B86">
         <v>85</v>
       </c>
-    </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C86">
+        <v>38</v>
+      </c>
+      <c r="D86">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A87">
         <v>1</v>
       </c>
       <c r="B87">
         <v>86</v>
       </c>
-    </row>
-    <row r="88" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C87">
+        <v>10</v>
+      </c>
+      <c r="D87">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A88">
         <v>1</v>
       </c>
       <c r="B88">
         <v>87</v>
       </c>
-    </row>
-    <row r="89" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C88">
+        <v>4</v>
+      </c>
+      <c r="D88">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A89">
         <v>1</v>
       </c>
       <c r="B89">
         <v>88</v>
       </c>
-    </row>
-    <row r="90" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C89">
+        <v>19</v>
+      </c>
+      <c r="D89">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A90">
         <v>1</v>
       </c>
       <c r="B90">
         <v>89</v>
       </c>
-    </row>
-    <row r="91" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C90">
+        <v>52</v>
+      </c>
+      <c r="D90">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A91">
         <v>1</v>
       </c>
       <c r="B91">
         <v>90</v>
       </c>
-    </row>
-    <row r="92" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C91">
+        <v>41</v>
+      </c>
+      <c r="D91">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A92">
         <v>1</v>
       </c>
       <c r="B92">
         <v>91</v>
       </c>
-    </row>
-    <row r="93" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C92">
+        <v>16</v>
+      </c>
+      <c r="D92">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A93">
         <v>1</v>
       </c>
       <c r="B93">
         <v>92</v>
       </c>
-    </row>
-    <row r="94" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C93">
+        <v>63</v>
+      </c>
+      <c r="D93">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A94">
         <v>1</v>
       </c>
       <c r="B94">
         <v>93</v>
       </c>
-    </row>
-    <row r="95" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C94">
+        <v>15</v>
+      </c>
+      <c r="D94">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A95">
         <v>1</v>
       </c>
       <c r="B95">
         <v>94</v>
       </c>
-    </row>
-    <row r="96" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C95">
+        <v>2</v>
+      </c>
+      <c r="D95">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="96" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A96">
         <v>1</v>
       </c>
       <c r="B96">
         <v>95</v>
       </c>
-    </row>
-    <row r="97" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C96">
+        <v>33</v>
+      </c>
+      <c r="D96">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A97">
         <v>1</v>
       </c>
       <c r="B97">
         <v>96</v>
       </c>
-    </row>
-    <row r="98" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C97">
+        <v>60</v>
+      </c>
+      <c r="D97">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="98" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A98">
         <v>1</v>
       </c>
       <c r="B98">
         <v>97</v>
       </c>
-    </row>
-    <row r="99" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C98">
+        <v>18</v>
+      </c>
+      <c r="D98">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="99" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A99">
         <v>1</v>
       </c>
       <c r="B99">
         <v>98</v>
       </c>
-    </row>
-    <row r="100" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C99">
+        <v>57</v>
+      </c>
+      <c r="D99">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="100" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A100">
         <v>1</v>
       </c>
       <c r="B100">
         <v>99</v>
       </c>
-    </row>
-    <row r="101" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C100">
+        <v>23</v>
+      </c>
+      <c r="D100">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="101" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A101">
         <v>1</v>
       </c>
       <c r="B101">
         <v>100</v>
+      </c>
+      <c r="C101">
+        <v>50</v>
+      </c>
+      <c r="D101">
+        <v>19</v>
       </c>
     </row>
   </sheetData>
